--- a/kobo_ficha_predial/FP_Ficha_Predial_Completa_KOBO.xlsx
+++ b/kobo_ficha_predial/FP_Ficha_Predial_Completa_KOBO.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2288,90 +2288,100 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_one posicion_sus</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>g_predio</t>
+          <t>posicion_sus_campo</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Posición del lote SUS declarada en campo</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>${tipo_unidad}='lote_sus'</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>geoshape</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>g_matriz</t>
+          <t>poligono_sus</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4. Descripción del predio matriz</t>
+          <t>Lote SUS – polígono</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Recorra el perímetro del lote SUS; mínimo 1 ha, ≤ 10 % del bloque, dentro o a ≤ 50 m.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>${tipo_unidad}='lote_sus'</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>select_one uso_actual</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>uso_actual</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Uso actual del suelo</t>
+          <t>g_predio</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>uso_otro</t>
+          <t>g_matriz</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Especifique el otro uso</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>${uso_actual}='otro'</t>
+          <t>4. Descripción del predio matriz</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>select_one ocupacion</t>
+          <t>select_one uso_actual</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ocupacion</t>
+          <t>uso_actual</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ocupación observada</t>
+          <t>Uso actual del suelo</t>
         </is>
       </c>
     </row>
@@ -2383,29 +2393,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ocupacion_det</t>
+          <t>uso_otro</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Detalle de la ocupación</t>
+          <t>Especifique el otro uso</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>${uso_actual}='otro'</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>select_multiple edificaciones</t>
+          <t>select_one ocupacion</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>edificaciones</t>
+          <t>ocupacion</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Edificaciones / cultivos</t>
+          <t>Ocupación observada</t>
         </is>
       </c>
     </row>
@@ -2417,195 +2437,185 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>edif_det</t>
+          <t>ocupacion_det</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Detalle / especifique «Otro»</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>selected(${edificaciones}, 'otro')</t>
+          <t>Detalle de la ocupación</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>select_one pendiente</t>
+          <t>select_multiple edificaciones</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>pendiente_clase</t>
+          <t>edificaciones</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Topografía / pendiente</t>
+          <t>Edificaciones / cultivos</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>aviso_pendiente</t>
+          <t>edif_det</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>⚠ Pendiente mayor a 75 %: fuera del criterio de idoneidad del proyecto.</t>
+          <t>Detalle / especifique «Otro»</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>${pendiente_clase}='extremadamente_empinada_75'</t>
+          <t>selected(${edificaciones}, 'otro')</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>select_multiple erosion</t>
+          <t>select_one pendiente</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>erosion</t>
+          <t>pendiente_clase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Erosión observada</t>
+          <t>Topografía / pendiente</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>select_one cobertura</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>aviso_pendiente</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Estado de la cobertura vegetal</t>
+          <t>⚠ Pendiente mayor a 75 %: fuera del criterio de idoneidad del proyecto.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>${pendiente_clase}='extremadamente_empinada_75'</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>select_one si_no</t>
+          <t>select_multiple erosion</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>mov_masa</t>
+          <t>erosion</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Evidencia de movimientos en masa</t>
+          <t>Erosión observada</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one cobertura</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>descripcion_predio</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Otros / descripción del predio</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Cobertura, pendiente, accesos, linderos, signos de degradación o de movimientos en masa.</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Estado de la cobertura vegetal</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>select_one tipo_predio</t>
+          <t>select_one si_no</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>tipo_predio</t>
+          <t>mov_masa</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tipo de predio</t>
+          <t>Evidencia de movimientos en masa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>predio_area_decl_ha</t>
+          <t>descripcion_predio</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Área matriz del predio (ha)</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Valor no negativo</t>
+          <t>Otros / descripción del predio</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Cobertura, pendiente, accesos, linderos, signos de degradación o de movimientos en masa.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one tipo_predio</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>predio_area_m2</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>if(${predio_area_decl_ha} != '', ${predio_area_decl_ha} * 10000, '')</t>
+          <t>tipo_predio</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tipo de predio</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2627,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>perimetro_m</t>
+          <t>predio_area_decl_ha</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Perímetro (m)</t>
+          <t>Área matriz del predio (ha)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -2639,68 +2649,78 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>g_matriz</t>
+          <t>predio_area_m2</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>if(${predio_area_decl_ha} != '', ${predio_area_decl_ha} * 10000, '')</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>g_colindancias</t>
+          <t>perimetro_m</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>4.2 Colindancias</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>field-list</t>
+          <t>Perímetro (m)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Valor no negativo</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>col_norte</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Colindante NORTE</t>
+          <t>g_matriz</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>select_one tipo_colindante</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>col_norte_tipo</t>
+          <t>g_colindancias</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tipo de colindante NORTE</t>
+          <t>4.2 Colindancias</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>field-list</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2732,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>col_este</t>
+          <t>col_norte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Colindante ESTE</t>
+          <t>Colindante NORTE</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2749,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>col_este_tipo</t>
+          <t>col_norte_tipo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tipo de colindante ESTE</t>
+          <t>Tipo de colindante NORTE</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2766,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>col_sur</t>
+          <t>col_este</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Colindante SUR</t>
+          <t>Colindante ESTE</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2783,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>col_sur_tipo</t>
+          <t>col_este_tipo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tipo de colindante SUR</t>
+          <t>Tipo de colindante ESTE</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2800,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>col_oeste</t>
+          <t>col_sur</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Colindante OESTE</t>
+          <t>Colindante SUR</t>
         </is>
       </c>
     </row>
@@ -2797,504 +2817,499 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>col_oeste_tipo</t>
+          <t>col_sur_tipo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tipo de colindante OESTE</t>
+          <t>Tipo de colindante SUR</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>g_colindancias</t>
+          <t>col_oeste</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Colindante OESTE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one tipo_colindante</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>conflicto_linderos_det</t>
+          <t>col_oeste_tipo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Conflictos de linderos / observaciones</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Tipo de colindante OESTE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>g_area</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>5. Descripción del área a intervenir (dentro de la unidad)</t>
+          <t>g_colindancias</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>predio_area_unidad_ha</t>
+          <t>conflicto_linderos_det</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Área del predio dentro de la unidad (ha)</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>string-length(${predio_area_decl_ha}) = 0 or (. &gt;= 0 and . &lt;= ${predio_area_decl_ha})</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>No puede superar el área matriz del predio</t>
+          <t>Conflictos de linderos / observaciones</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>pct_predio</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>if(${predio_area_decl_ha} &gt; 0 and ${predio_area_unidad_ha} != '', round(100 * ${predio_area_unidad_ha} div ${predio_area_decl_ha}, 1), '')</t>
+          <t>g_area</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>5. Descripción del área a intervenir (dentro de la unidad)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>nota_pct</t>
+          <t>predio_area_unidad_ha</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Área dentro de la unidad: ${pct_predio} % del predio matriz.</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>${pct_predio} != ''</t>
+          <t>Área del predio dentro de la unidad (ha)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>string-length(${predio_area_decl_ha}) = 0 or (. &gt;= 0 and . &lt;= ${predio_area_decl_ha})</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>No puede superar el área matriz del predio</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>select_multiple interferencias</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>interferencias</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Interferencias</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>«Ninguna» no se combina con otras opciones</t>
+          <t>pct_predio</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>if(${predio_area_decl_ha} &gt; 0 and ${predio_area_unidad_ha} != '', round(100 * ${predio_area_unidad_ha} div ${predio_area_decl_ha}, 1), '')</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>interf_detalle</t>
+          <t>nota_pct</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Detalle de interferencias</t>
+          <t>Área dentro de la unidad: ${pct_predio} % del predio matriz.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>${interferencias} != '' and not(selected(${interferencias}, 'ninguna'))</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>${pct_predio} != ''</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>select_multiple intervencion</t>
+          <t>select_multiple interferencias</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>intervencion_prevista</t>
+          <t>interferencias</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Intervención prevista (referencial)</t>
+          <t>Interferencias</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>«Ninguna» no se combina con otras opciones</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>select_one si_no</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tiene_afectaciones</t>
+          <t>interf_detalle</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>¿Existen obras o bienes afectados en el área?</t>
+          <t>Detalle de interferencias</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>${interferencias} != '' and not(selected(${interferencias}, 'ninguna'))</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>select_multiple intervencion</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>g_area</t>
+          <t>intervencion_prevista</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Intervención prevista (referencial)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>select_one si_no</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>r_afectaciones</t>
+          <t>tiene_afectaciones</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Afectaciones (OC-01, OC-02…)</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>${tiene_afectaciones}='si'</t>
+          <t>¿Existen obras o bienes afectados en el área?</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>af_codigo</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>concat('OC-', if(position(..) &lt; 10, '0', ''), position(..))</t>
+          <t>g_area</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>af_nota</t>
+          <t>r_afectaciones</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>**${af_codigo}**</t>
+          <t>Afectaciones (OC-01, OC-02…)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>${tiene_afectaciones}='si'</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>af_descripcion</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Descripción / uso</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>af_codigo</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>concat('OC-', if(position(..) &lt; 10, '0', ''), position(..))</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>af_metrado</t>
+          <t>af_nota</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Metrado</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Valor no negativo</t>
+          <t>**${af_codigo}**</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>select_one und_medida</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>af_und</t>
+          <t>af_descripcion</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Unidad de medida</t>
+          <t>Descripción / uso</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>select_one material</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>af_material</t>
+          <t>af_metrado</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Material predominante</t>
+          <t>Metrado</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Valor no negativo</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>select_one conservacion</t>
+          <t>select_one und_medida</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>af_conservacion</t>
+          <t>af_und</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Estado de conservación</t>
+          <t>Unidad de medida</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>select_one construccion</t>
+          <t>select_one material</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>af_construccion</t>
+          <t>af_material</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Estado de construcción</t>
+          <t>Material predominante</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one conservacion</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>af_ubicacion</t>
+          <t>af_conservacion</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ubicación en el predio</t>
+          <t>Estado de conservación</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>select_one construccion</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>r_afectaciones</t>
+          <t>af_construccion</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Estado de construcción</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>g_liberacion</t>
+          <t>af_ubicacion</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>6. Disponibilidad y condición de liberación</t>
+          <t>Ubicación en el predio</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>select_one aceptacion</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>aceptacion</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Aceptación del titular / prediante</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>r_afectaciones</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>select_one modalidad</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>modalidad</t>
+          <t>g_liberacion</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Modalidad de disponibilidad</t>
+          <t>6. Disponibilidad y condición de liberación</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>select_one conclusion_campo</t>
+          <t>select_one aceptacion</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>conclusion_campo</t>
+          <t>aceptacion</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Conclusión de campo</t>
+          <t>Aceptación del titular / prediante</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -3306,295 +3321,280 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>select_one estado_la</t>
+          <t>select_one modalidad</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>estado_la_propuesto</t>
+          <t>modalidad</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Estado LA propuesto</t>
+          <t>Modalidad de disponibilidad</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>select_one tipo_acta</t>
+          <t>select_one conclusion_campo</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>tipo_acta_prevista</t>
+          <t>conclusion_campo</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Acta prevista</t>
+          <t>Conclusión de campo</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one estado_la</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>cod_titular_prev</t>
+          <t>estado_la_propuesto</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Código de titular ya registrado (T0000), si existe</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>regex(., '^T[0-9]{4}$')</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Formato T0000 (T y 4 dígitos)</t>
+          <t>Estado LA propuesto</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one tipo_acta</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>alertas</t>
+          <t>tipo_acta_prevista</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Observaciones / alertas sociales</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Acta prevista</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>g_liberacion</t>
+          <t>cod_titular_prev</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Código de titular ya registrado (T0000), si existe</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>regex(., '^T[0-9]{4}$')</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Formato T0000 (T y 4 dígitos)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>g_croquis</t>
+          <t>alertas</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7. Croquis del predio y puntos de control</t>
+          <t>Observaciones / alertas sociales</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>croquis</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Croquis del predio (dibuje: norte, linderos, accesos, vértices)</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>max-pixels=1280</t>
+          <t>g_liberacion</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>g_croquis</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>7. Croquis del predio y puntos de control</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>r_puntos</t>
+          <t>croquis</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Puntos de control / vértices del predio</t>
+          <t>Croquis del predio (dibuje: norte, linderos, accesos, vértices)</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>max-pixels=1280</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>pt_gps</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Precisión ≤ 10 m.</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>g_croquis</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>select_one pt_tipo</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>pt_tipo</t>
+          <t>r_puntos</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tipo de punto</t>
+          <t>Puntos de control / vértices del predio</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>r_puntos</t>
+          <t>pt_gps</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Punto</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Precisión ≤ 10 m.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one pt_tipo</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>g_fotos</t>
+          <t>pt_tipo</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>8. Panel fotográfico</t>
+          <t>Tipo de punto</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>foto_1</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Foto 1 – Vista general del predio</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Tome la foto con la cámara del celular (o elija una imagen).</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>max-pixels=1280</t>
+          <t>r_puntos</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>foto_2</t>
+          <t>g_fotos</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Foto 2 – Cobertura vegetal / uso actual</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Tome la foto con la cámara del celular (o elija una imagen).</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>max-pixels=1280</t>
+          <t>8. Panel fotográfico</t>
         </is>
       </c>
     </row>
@@ -3606,12 +3606,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>foto_3</t>
+          <t>foto_1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Foto 3 – Linderos, hitos o accesos</t>
+          <t>Foto 1 – Vista general del predio</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>foto_4</t>
+          <t>foto_2</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Foto 4 – Interferencias o detalle relevante</t>
+          <t>Foto 2 – Cobertura vegetal / uso actual</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3655,110 +3655,164 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>g_fotos</t>
+          <t>foto_3</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Foto 3 – Linderos, hitos o accesos</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Tome la foto con la cámara del celular (o elija una imagen).</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>max-pixels=1280</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>g_firmas</t>
+          <t>foto_4</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>9. Conformidad</t>
+          <t>Foto 4 – Interferencias o detalle relevante</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Tome la foto con la cámara del celular (o elija una imagen).</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>max-pixels=1280</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>firma_prediante</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Firma del prediante / titular (conformidad)</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>${consentimiento}='si'</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>max-pixels=800</t>
+          <t>g_fotos</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>lugar</t>
+          <t>g_firmas</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Lugar</t>
+          <t>9. Conformidad</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>g_firmas</t>
+          <t>firma_prediante</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Firma del prediante / titular (conformidad)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>${consentimiento}='si'</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>signature</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>max-pixels=800</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>lugar</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Lugar</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>g_firmas</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>nota_fin</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>Fin de la ficha predial. Pulse «Enviar»: el formulario queda en blanco y vuelve al inicio para registrar el siguiente predio.</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>Use el enlace «En línea-Fuera de línea (envíos múltiples)» de KoboToolbox o KoboCollect.</t>
         </is>
@@ -3775,7 +3829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3962,34 +4016,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tipo_titularidad</t>
+          <t>posicion_sus</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comunal</t>
+          <t>DENTRO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Comunidad campesina</t>
+          <t>Dentro del bloque</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tipo_titularidad</t>
+          <t>posicion_sus</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>privado</t>
+          <t>CONTIGUO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Privado (con título)</t>
+          <t>Contiguo (≤ 50 m)</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4055,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>posesionario</t>
+          <t>comunal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Posesionario</t>
+          <t>Comunidad campesina</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4072,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ocupante</t>
+          <t>privado</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ocupante</t>
+          <t>Privado (con título)</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4089,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sucesion</t>
+          <t>posesionario</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sucesión</t>
+          <t>Posesionario</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4106,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>estatal</t>
+          <t>ocupante</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estatal</t>
+          <t>Ocupante</t>
         </is>
       </c>
     </row>
@@ -4069,46 +4123,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sin_titular</t>
+          <t>sucesion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sin titular / en conflicto</t>
+          <t>Sucesión</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sucesion_estado</t>
+          <t>tipo_titularidad</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>declarada</t>
+          <t>estatal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sucesión declarada</t>
+          <t>Estatal</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sucesion_estado</t>
+          <t>tipo_titularidad</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>en_tramite</t>
+          <t>sin_titular</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>Sin titular / en conflicto</t>
         </is>
       </c>
     </row>
@@ -4120,46 +4174,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sin_tramite</t>
+          <t>declarada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sin trámite</t>
+          <t>Sucesión declarada</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>estado_civil</t>
+          <t>sucesion_estado</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>soltero</t>
+          <t>en_tramite</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Soltero(a)</t>
+          <t>En trámite</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>estado_civil</t>
+          <t>sucesion_estado</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>casado</t>
+          <t>sin_tramite</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Casado(a)</t>
+          <t>Sin trámite</t>
         </is>
       </c>
     </row>
@@ -4171,12 +4225,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>conviviente</t>
+          <t>soltero</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Conviviente</t>
+          <t>Soltero(a)</t>
         </is>
       </c>
     </row>
@@ -4188,12 +4242,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>viudo</t>
+          <t>casado</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Viudo(a)</t>
+          <t>Casado(a)</t>
         </is>
       </c>
     </row>
@@ -4205,46 +4259,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>divorciado</t>
+          <t>conviviente</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Divorciado(a)</t>
+          <t>Conviviente</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>docs_exhibidos</t>
+          <t>estado_civil</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>titulo</t>
+          <t>viudo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Título de propiedad</t>
+          <t>Viudo(a)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>docs_exhibidos</t>
+          <t>estado_civil</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>partida</t>
+          <t>divorciado</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Partida registral</t>
+          <t>Divorciado(a)</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4310,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>constancia_posesion</t>
+          <t>titulo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Constancia de posesión</t>
+          <t>Título de propiedad</t>
         </is>
       </c>
     </row>
@@ -4273,12 +4327,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>certificado_posesion</t>
+          <t>partida</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Certificado de posesión</t>
+          <t>Partida registral</t>
         </is>
       </c>
     </row>
@@ -4290,12 +4344,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>acta_asamblea</t>
+          <t>constancia_posesion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Acta de asamblea</t>
+          <t>Constancia de posesión</t>
         </is>
       </c>
     </row>
@@ -4307,12 +4361,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>declaratoria_herederos</t>
+          <t>certificado_posesion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Declaratoria de herederos</t>
+          <t>Certificado de posesión</t>
         </is>
       </c>
     </row>
@@ -4324,12 +4378,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dni</t>
+          <t>acta_asamblea</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Acta de asamblea</t>
         </is>
       </c>
     </row>
@@ -4341,46 +4395,46 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>declaratoria_herederos</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Declaratoria de herederos</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>uso_actual</t>
+          <t>docs_exhibidos</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bosque_seco</t>
+          <t>dni</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bosque seco</t>
+          <t>DNI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>uso_actual</t>
+          <t>docs_exhibidos</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>matorral</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Matorral</t>
+          <t>Ninguno</t>
         </is>
       </c>
     </row>
@@ -4392,12 +4446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>pastizal</t>
+          <t>bosque_seco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pastizal / pastoreo</t>
+          <t>Bosque seco</t>
         </is>
       </c>
     </row>
@@ -4409,12 +4463,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>agricola</t>
+          <t>matorral</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Agrícola</t>
+          <t>Matorral</t>
         </is>
       </c>
     </row>
@@ -4426,12 +4480,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>purma</t>
+          <t>pastizal</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Purma / descanso</t>
+          <t>Pastizal / pastoreo</t>
         </is>
       </c>
     </row>
@@ -4443,12 +4497,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eriazo</t>
+          <t>agricola</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eriazo / suelo desnudo</t>
+          <t>Agrícola</t>
         </is>
       </c>
     </row>
@@ -4460,46 +4514,46 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>purma</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Purma / descanso</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ocupacion</t>
+          <t>uso_actual</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>sin_ocupacion</t>
+          <t>eriazo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sin ocupación</t>
+          <t>Eriazo / suelo desnudo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ocupacion</t>
+          <t>uso_actual</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>pastoreo</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pastoreo</t>
+          <t>Otro</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4565,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>cultivo</t>
+          <t>sin_ocupacion</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cultivo</t>
+          <t>Sin ocupación</t>
         </is>
       </c>
     </row>
@@ -4528,12 +4582,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>vivienda</t>
+          <t>pastoreo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Pastoreo</t>
         </is>
       </c>
     </row>
@@ -4545,46 +4599,46 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>mixta</t>
+          <t>cultivo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Cultivo</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>acceso_tipo</t>
+          <t>ocupacion</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>carretera</t>
+          <t>vivienda</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Carretera</t>
+          <t>Vivienda</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>acceso_tipo</t>
+          <t>ocupacion</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>trocha</t>
+          <t>mixta</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Trocha carrozable</t>
+          <t>Mixta</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4650,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>herradura</t>
+          <t>carretera</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Camino de herradura</t>
+          <t>Carretera</t>
         </is>
       </c>
     </row>
@@ -4613,46 +4667,46 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>sin_camino</t>
+          <t>trocha</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sin camino</t>
+          <t>Trocha carrozable</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>interferencias</t>
+          <t>acceso_tipo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ninguna</t>
+          <t>herradura</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t>Camino de herradura</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>interferencias</t>
+          <t>acceso_tipo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>bosque_natural</t>
+          <t>sin_camino</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bosque natural</t>
+          <t>Sin camino</t>
         </is>
       </c>
     </row>
@@ -4664,12 +4718,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>cultivos</t>
+          <t>ninguna</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cultivos</t>
+          <t>Ninguna</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4735,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>vivienda</t>
+          <t>bosque_natural</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Bosque natural</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4752,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>infraestructura</t>
+          <t>cultivos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Cultivos</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4769,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>restos_arqueologicos</t>
+          <t>vivienda</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Restos arqueológicos</t>
+          <t>Vivienda</t>
         </is>
       </c>
     </row>
@@ -4732,12 +4786,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>concesion_minera</t>
+          <t>infraestructura</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Concesión minera</t>
+          <t>Infraestructura</t>
         </is>
       </c>
     </row>
@@ -4749,12 +4803,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>linea_electrica</t>
+          <t>restos_arqueologicos</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Línea eléctrica</t>
+          <t>Restos arqueológicos</t>
         </is>
       </c>
     </row>
@@ -4766,46 +4820,46 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>concesion_minera</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Concesión minera</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>aceptacion</t>
+          <t>interferencias</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>favorable</t>
+          <t>linea_electrica</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Línea eléctrica</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>aceptacion</t>
+          <t>interferencias</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>condicionada</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Condicionada</t>
+          <t>Otro</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4871,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>rechazo</t>
+          <t>favorable</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>Favorable</t>
         </is>
       </c>
     </row>
@@ -4834,46 +4888,46 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>sin_definir</t>
+          <t>condicionada</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sin definir</t>
+          <t>Condicionada</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>modalidad</t>
+          <t>aceptacion</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>donacion</t>
+          <t>rechazo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Donación</t>
+          <t>Rechazo</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>modalidad</t>
+          <t>aceptacion</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>cesion_uso</t>
+          <t>sin_definir</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cesión en uso</t>
+          <t>Sin definir</t>
         </is>
       </c>
     </row>
@@ -4885,12 +4939,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>convenio</t>
+          <t>donacion</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Convenio</t>
+          <t>Donación</t>
         </is>
       </c>
     </row>
@@ -4902,46 +4956,46 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>alquiler</t>
+          <t>cesion_uso</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alquiler</t>
+          <t>Cesión en uso</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>conclusion_campo</t>
+          <t>modalidad</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>sin_restriccion</t>
+          <t>convenio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sin restricción</t>
+          <t>Convenio</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>conclusion_campo</t>
+          <t>modalidad</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>con_restriccion</t>
+          <t>alquiler</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Con restricción</t>
+          <t>Alquiler</t>
         </is>
       </c>
     </row>
@@ -4953,46 +5007,46 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>no_apto</t>
+          <t>sin_restriccion</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>No apto</t>
+          <t>Sin restricción</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>estado_la</t>
+          <t>conclusion_campo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LA-0</t>
+          <t>con_restriccion</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LA-0</t>
+          <t>Con restricción</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>estado_la</t>
+          <t>conclusion_campo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LA-1</t>
+          <t>no_apto</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LA-1</t>
+          <t>No apto</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5058,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LA-2</t>
+          <t>LA-0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LA-2</t>
+          <t>LA-0</t>
         </is>
       </c>
     </row>
@@ -5021,12 +5075,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LA-3</t>
+          <t>LA-1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LA-3</t>
+          <t>LA-1</t>
         </is>
       </c>
     </row>
@@ -5038,12 +5092,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LA-4</t>
+          <t>LA-2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LA-4</t>
+          <t>LA-2</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5109,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LA-5</t>
+          <t>LA-3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LA-5</t>
+          <t>LA-3</t>
         </is>
       </c>
     </row>
@@ -5072,46 +5126,46 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LA-6</t>
+          <t>LA-4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LA-6</t>
+          <t>LA-4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>tipo_acta</t>
+          <t>estado_la</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A-03</t>
+          <t>LA-5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>A-03 · Acta de asamblea comunal</t>
+          <t>LA-5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>tipo_acta</t>
+          <t>estado_la</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A-04</t>
+          <t>LA-6</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>A-04 · Acta del titular / posesionario</t>
+          <t>LA-6</t>
         </is>
       </c>
     </row>
@@ -5123,46 +5177,46 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A-07</t>
+          <t>A-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>A-07 · Acta de terreno para vivero</t>
+          <t>A-03 · Acta de asamblea comunal</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>pt_tipo</t>
+          <t>tipo_acta</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>vertice</t>
+          <t>A-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Vértice</t>
+          <t>A-04 · Acta del titular / posesionario</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>pt_tipo</t>
+          <t>tipo_acta</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>hito</t>
+          <t>A-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hito</t>
+          <t>A-07 · Acta de terreno para vivero</t>
         </is>
       </c>
     </row>
@@ -5174,80 +5228,80 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>referencia</t>
+          <t>vertice</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Punto de referencia</t>
+          <t>Vértice</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>personeria</t>
+          <t>pt_tipo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>natural</t>
+          <t>hito</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Hito</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>personeria</t>
+          <t>pt_tipo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>juridica</t>
+          <t>referencia</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jurídica</t>
+          <t>Punto de referencia</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>sit_registral</t>
+          <t>personeria</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>inscrito_en_sunarp</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Inscrito en SUNARP</t>
+          <t>Natural</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>sit_registral</t>
+          <t>personeria</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>no_inscrito</t>
+          <t>juridica</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No inscrito</t>
+          <t>Jurídica</t>
         </is>
       </c>
     </row>
@@ -5259,12 +5313,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>en_tramite_de_inscripcion</t>
+          <t>inscrito_en_sunarp</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>En trámite de inscripción</t>
+          <t>Inscrito en SUNARP</t>
         </is>
       </c>
     </row>
@@ -5276,46 +5330,46 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>por_verificar</t>
+          <t>no_inscrito</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Por verificar</t>
+          <t>No inscrito</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>cargo_rep</t>
+          <t>sit_registral</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>presidente_comunal</t>
+          <t>en_tramite_de_inscripcion</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Presidente comunal</t>
+          <t>En trámite de inscripción</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>cargo_rep</t>
+          <t>sit_registral</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>representante_legal</t>
+          <t>por_verificar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Representante legal</t>
+          <t>Por verificar</t>
         </is>
       </c>
     </row>
@@ -5327,12 +5381,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>apoderado</t>
+          <t>presidente_comunal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Apoderado</t>
+          <t>Presidente comunal</t>
         </is>
       </c>
     </row>
@@ -5344,12 +5398,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>funcionario_publico</t>
+          <t>representante_legal</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Funcionario público</t>
+          <t>Representante legal</t>
         </is>
       </c>
     </row>
@@ -5361,46 +5415,46 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>apoderado</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Apoderado</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tipo_predio</t>
+          <t>cargo_rep</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>rustico</t>
+          <t>funcionario_publico</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rústico</t>
+          <t>Funcionario público</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>tipo_predio</t>
+          <t>cargo_rep</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>eriazo</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Eriazo</t>
+          <t>Otro</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5466,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>urbano</t>
+          <t>rustico</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Urbano</t>
+          <t>Rústico</t>
         </is>
       </c>
     </row>
@@ -5429,46 +5483,46 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>por_verificar</t>
+          <t>eriazo</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Por verificar</t>
+          <t>Eriazo</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>edificaciones</t>
+          <t>tipo_predio</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ninguna</t>
+          <t>urbano</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t>Urbano</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>edificaciones</t>
+          <t>tipo_predio</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>vivienda</t>
+          <t>por_verificar</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Por verificar</t>
         </is>
       </c>
     </row>
@@ -5480,12 +5534,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>corral_cobertizo</t>
+          <t>ninguna</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Corral / cobertizo</t>
+          <t>Ninguna</t>
         </is>
       </c>
     </row>
@@ -5497,12 +5551,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>cultivos_anuales</t>
+          <t>vivienda</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cultivos anuales</t>
+          <t>Vivienda</t>
         </is>
       </c>
     </row>
@@ -5514,12 +5568,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>cultivos_permanentes_frutales</t>
+          <t>corral_cobertizo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cultivos permanentes / frutales</t>
+          <t>Corral / cobertizo</t>
         </is>
       </c>
     </row>
@@ -5531,12 +5585,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>cercos</t>
+          <t>cultivos_anuales</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cercos</t>
+          <t>Cultivos anuales</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5602,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>pozo_reservorio</t>
+          <t>cultivos_permanentes_frutales</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pozo / reservorio</t>
+          <t>Cultivos permanentes / frutales</t>
         </is>
       </c>
     </row>
@@ -5565,46 +5619,46 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>cercos</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Cercos</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>edificaciones</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>plana_04</t>
+          <t>pozo_reservorio</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Plana (0–4 %)</t>
+          <t>Pozo / reservorio</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>edificaciones</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>moderada_415</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Moderada (4–15 %)</t>
+          <t>Otro</t>
         </is>
       </c>
     </row>
@@ -5616,12 +5670,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>fuerte_1525</t>
+          <t>plana_04</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fuerte (15–25 %)</t>
+          <t>Plana (0–4 %)</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5687,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>empinada_2550</t>
+          <t>moderada_415</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Empinada (25–50 %)</t>
+          <t>Moderada (4–15 %)</t>
         </is>
       </c>
     </row>
@@ -5650,12 +5704,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>muy_empinada_5075</t>
+          <t>fuerte_1525</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Muy empinada (50–75 %)</t>
+          <t>Fuerte (15–25 %)</t>
         </is>
       </c>
     </row>
@@ -5667,46 +5721,46 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>extremadamente_empinada_75</t>
+          <t>empinada_2550</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Extremadamente empinada (&gt; 75 %)</t>
+          <t>Empinada (25–50 %)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>erosion</t>
+          <t>pendiente</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>sin_erosion_visible</t>
+          <t>muy_empinada_5075</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sin erosión visible</t>
+          <t>Muy empinada (50–75 %)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>erosion</t>
+          <t>pendiente</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>laminar</t>
+          <t>extremadamente_empinada_75</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Laminar</t>
+          <t>Extremadamente empinada (&gt; 75 %)</t>
         </is>
       </c>
     </row>
@@ -5718,12 +5772,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>en_surcos</t>
+          <t>sin_erosion_visible</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>En surcos</t>
+          <t>Sin erosión visible</t>
         </is>
       </c>
     </row>
@@ -5735,12 +5789,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>en_carcavas</t>
+          <t>laminar</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>En cárcavas</t>
+          <t>Laminar</t>
         </is>
       </c>
     </row>
@@ -5752,46 +5806,46 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>movimientos_en_masa</t>
+          <t>en_surcos</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Movimientos en masa</t>
+          <t>En surcos</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>erosion</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>bosque_seco_conservado</t>
+          <t>en_carcavas</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosque seco conservado</t>
+          <t>En cárcavas</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>erosion</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>bosque_seco_intervenido_ralo</t>
+          <t>movimientos_en_masa</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosque seco intervenido / ralo</t>
+          <t>Movimientos en masa</t>
         </is>
       </c>
     </row>
@@ -5803,12 +5857,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>matorral</t>
+          <t>bosque_seco_conservado</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Matorral</t>
+          <t>Bosque seco conservado</t>
         </is>
       </c>
     </row>
@@ -5820,12 +5874,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>pastizal</t>
+          <t>bosque_seco_intervenido_ralo</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pastizal</t>
+          <t>Bosque seco intervenido / ralo</t>
         </is>
       </c>
     </row>
@@ -5837,46 +5891,46 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>suelo_desnudo_degradado</t>
+          <t>matorral</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Suelo desnudo / degradado</t>
+          <t>Matorral</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>tipo_colindante</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>predio_privado</t>
+          <t>pastizal</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Predio privado</t>
+          <t>Pastizal</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>tipo_colindante</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>comunidad_campesina</t>
+          <t>suelo_desnudo_degradado</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Comunidad campesina</t>
+          <t>Suelo desnudo / degradado</t>
         </is>
       </c>
     </row>
@@ -5888,12 +5942,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>terreno_del_estado</t>
+          <t>predio_privado</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Terreno del Estado</t>
+          <t>Predio privado</t>
         </is>
       </c>
     </row>
@@ -5905,12 +5959,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>quebrada_rio</t>
+          <t>comunidad_campesina</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Quebrada / río</t>
+          <t>Comunidad campesina</t>
         </is>
       </c>
     </row>
@@ -5922,12 +5976,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>camino_trocha</t>
+          <t>terreno_del_estado</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Camino / trocha</t>
+          <t>Terreno del Estado</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5993,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>divisoria_cerro</t>
+          <t>quebrada_rio</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Divisoria / cerro</t>
+          <t>Quebrada / río</t>
         </is>
       </c>
     </row>
@@ -5956,46 +6010,46 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>camino_trocha</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Camino / trocha</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>und_medida</t>
+          <t>tipo_colindante</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>divisoria_cerro</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Divisoria / cerro</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>und_medida</t>
+          <t>tipo_colindante</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>Otro</t>
         </is>
       </c>
     </row>
@@ -6007,12 +6061,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
     </row>
@@ -6024,12 +6078,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m²</t>
         </is>
       </c>
     </row>
@@ -6041,46 +6095,46 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m³</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>und_medida</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>madera</t>
+          <t>und</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Madera</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>und_medida</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>adobe</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>ha</t>
         </is>
       </c>
     </row>
@@ -6092,12 +6146,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>tapial</t>
+          <t>madera</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tapial</t>
+          <t>Madera</t>
         </is>
       </c>
     </row>
@@ -6109,12 +6163,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>piedra</t>
+          <t>adobe</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Piedra</t>
+          <t>Adobe</t>
         </is>
       </c>
     </row>
@@ -6126,12 +6180,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>concreto</t>
+          <t>tapial</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Concreto</t>
+          <t>Tapial</t>
         </is>
       </c>
     </row>
@@ -6143,12 +6197,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>acero_metal</t>
+          <t>piedra</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Acero / metal</t>
+          <t>Piedra</t>
         </is>
       </c>
     </row>
@@ -6160,12 +6214,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>alambre_de_puas</t>
+          <t>concreto</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Alambre de púas</t>
+          <t>Concreto</t>
         </is>
       </c>
     </row>
@@ -6177,12 +6231,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>malla</t>
+          <t>acero_metal</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Malla</t>
+          <t>Acero / metal</t>
         </is>
       </c>
     </row>
@@ -6194,12 +6248,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>calamina</t>
+          <t>alambre_de_puas</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Calamina</t>
+          <t>Alambre de púas</t>
         </is>
       </c>
     </row>
@@ -6211,46 +6265,46 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>malla</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Malla</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>conservacion</t>
+          <t>material</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>bueno</t>
+          <t>calamina</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bueno</t>
+          <t>Calamina</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>conservacion</t>
+          <t>material</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>Otro</t>
         </is>
       </c>
     </row>
@@ -6262,46 +6316,46 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>malo</t>
+          <t>bueno</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Malo</t>
+          <t>Bueno</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>construccion</t>
+          <t>conservacion</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>terminado</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Terminado</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>construccion</t>
+          <t>conservacion</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>en_construccion</t>
+          <t>malo</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>En construcción</t>
+          <t>Malo</t>
         </is>
       </c>
     </row>
@@ -6313,46 +6367,46 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>abandonado</t>
+          <t>terminado</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Abandonado</t>
+          <t>Terminado</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>intervencion</t>
+          <t>construccion</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>revegetacion_con_especies_nativas</t>
+          <t>en_construccion</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Revegetación con especies nativas</t>
+          <t>En construcción</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>intervencion</t>
+          <t>construccion</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>reforestacion_con_especies_nativas</t>
+          <t>abandonado</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Reforestación con especies nativas</t>
+          <t>Abandonado</t>
         </is>
       </c>
     </row>
@@ -6364,12 +6418,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>zanjas_de_infiltracion</t>
+          <t>revegetacion_con_especies_nativas</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Zanjas de infiltración</t>
+          <t>Revegetación con especies nativas</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6435,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>terrazas_de_formacion_lenta</t>
+          <t>reforestacion_con_especies_nativas</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Terrazas de formación lenta</t>
+          <t>Reforestación con especies nativas</t>
         </is>
       </c>
     </row>
@@ -6398,12 +6452,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>diques_para_control_de_carcavas</t>
+          <t>zanjas_de_infiltracion</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Diques para control de cárcavas</t>
+          <t>Zanjas de infiltración</t>
         </is>
       </c>
     </row>
@@ -6415,12 +6469,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>clausura_temporal_y_manejo_de_pastizales</t>
+          <t>terrazas_de_formacion_lenta</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Clausura temporal y manejo de pastizales</t>
+          <t>Terrazas de formación lenta</t>
         </is>
       </c>
     </row>
@@ -6432,12 +6486,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>barreras_vivas_cercos_vivos</t>
+          <t>diques_para_control_de_carcavas</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Barreras vivas / cercos vivos</t>
+          <t>Diques para control de cárcavas</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6503,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>vivero_temporal_o_de_aclimatacion</t>
+          <t>clausura_temporal_y_manejo_de_pastizales</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Vivero temporal o de aclimatación</t>
+          <t>Clausura temporal y manejo de pastizales</t>
         </is>
       </c>
     </row>
@@ -6466,12 +6520,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>obras_complementarias_estabilizacion_dre</t>
+          <t>barreras_vivas_cercos_vivos</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Obras complementarias (estabilización / drenaje)</t>
+          <t>Barreras vivas / cercos vivos</t>
         </is>
       </c>
     </row>
@@ -6483,63 +6537,63 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>por_definir</t>
+          <t>vivero_temporal_o_de_aclimatacion</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Por definir</t>
+          <t>Vivero temporal o de aclimatación</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>intervencion</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>piura</t>
+          <t>obras_complementarias_estabilizacion_dre</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Piura</t>
+          <t>Obras complementarias (estabilización / drenaje)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>dep_domicilio</t>
+          <t>intervencion</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>piura</t>
+          <t>por_definir</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Piura</t>
+          <t>Por definir</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>dep_domicilio</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>tumbes</t>
+          <t>piura</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tumbes</t>
+          <t>Piura</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6605,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>lambayeque</t>
+          <t>piura</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Lambayeque</t>
+          <t>Piura</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6622,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>cajamarca</t>
+          <t>tumbes</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Cajamarca</t>
+          <t>Tumbes</t>
         </is>
       </c>
     </row>
@@ -6585,12 +6639,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>lima</t>
+          <t>lambayeque</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Lambayeque</t>
         </is>
       </c>
     </row>
@@ -6602,46 +6656,46 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>cajamarca</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Cajamarca</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>prov_domicilio</t>
+          <t>dep_domicilio</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ayabaca</t>
+          <t>lima</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ayabaca</t>
+          <t>Lima</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>prov_domicilio</t>
+          <t>dep_domicilio</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>huancabamba</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Huancabamba</t>
+          <t>Otro</t>
         </is>
       </c>
     </row>
@@ -6653,12 +6707,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>morropon</t>
+          <t>ayabaca</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Morropón</t>
+          <t>Ayabaca</t>
         </is>
       </c>
     </row>
@@ -6670,12 +6724,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>piura</t>
+          <t>huancabamba</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Piura</t>
+          <t>Huancabamba</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6741,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>sullana</t>
+          <t>morropon</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sullana</t>
+          <t>Morropón</t>
         </is>
       </c>
     </row>
@@ -6704,12 +6758,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>paita</t>
+          <t>piura</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Paita</t>
+          <t>Piura</t>
         </is>
       </c>
     </row>
@@ -6721,12 +6775,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>talara</t>
+          <t>sullana</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Talara</t>
+          <t>Sullana</t>
         </is>
       </c>
     </row>
@@ -6738,12 +6792,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>sechura</t>
+          <t>paita</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Sechura</t>
+          <t>Paita</t>
         </is>
       </c>
     </row>
@@ -6755,46 +6809,46 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>talara</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Otra</t>
+          <t>Talara</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>prov_domicilio</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ayabaca</t>
+          <t>sechura</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ayabaca</t>
+          <t>Sechura</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>prov_domicilio</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>huancabamba</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Huancabamba</t>
+          <t>Otra</t>
         </is>
       </c>
     </row>
@@ -6806,56 +6860,46 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>morropon</t>
+          <t>ayabaca</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Morropón</t>
+          <t>Ayabaca</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>buenos_aires</t>
+          <t>huancabamba</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>morropon</t>
+          <t>Huancabamba</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>canchaque</t>
+          <t>morropon</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Canchaque</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>huancabamba</t>
+          <t>Morropón</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6911,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>chalaco</t>
+          <t>buenos_aires</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Chalaco</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -6889,17 +6933,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>chulucanas</t>
+          <t>canchaque</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Chulucanas</t>
+          <t>Canchaque</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>morropon</t>
+          <t>huancabamba</t>
         </is>
       </c>
     </row>
@@ -6911,17 +6955,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>frias</t>
+          <t>chalaco</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Frías</t>
+          <t>Chalaco</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ayabaca</t>
+          <t>morropon</t>
         </is>
       </c>
     </row>
@@ -6933,17 +6977,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>huancabamba</t>
+          <t>chulucanas</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Huancabamba</t>
+          <t>Chulucanas</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>huancabamba</t>
+          <t>morropon</t>
         </is>
       </c>
     </row>
@@ -6955,17 +6999,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>huarmaca</t>
+          <t>frias</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Huarmaca</t>
+          <t>Frías</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>huancabamba</t>
+          <t>ayabaca</t>
         </is>
       </c>
     </row>
@@ -6977,12 +7021,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>lalaquiz</t>
+          <t>huancabamba</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Lalaquiz</t>
+          <t>Huancabamba</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -6999,17 +7043,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>morropon</t>
+          <t>huarmaca</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Morropón</t>
+          <t>Huarmaca</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>morropon</t>
+          <t>huancabamba</t>
         </is>
       </c>
     </row>
@@ -7021,17 +7065,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>salitral</t>
+          <t>lalaquiz</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Salitral</t>
+          <t>Lalaquiz</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>morropon</t>
+          <t>huancabamba</t>
         </is>
       </c>
     </row>
@@ -7043,12 +7087,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>san_juan_de_bigote</t>
+          <t>morropon</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>San Juan de Bigote</t>
+          <t>Morropón</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -7065,17 +7109,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>san_miguel_de_el_faique</t>
+          <t>salitral</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>San Miguel de El Faique</t>
+          <t>Salitral</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>huancabamba</t>
+          <t>morropon</t>
         </is>
       </c>
     </row>
@@ -7087,12 +7131,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>santa_catalina_de_mossa</t>
+          <t>san_juan_de_bigote</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Santa Catalina de Mossa</t>
+          <t>San Juan de Bigote</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -7109,17 +7153,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>santo_domingo</t>
+          <t>san_miguel_de_el_faique</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>San Miguel de El Faique</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>morropon</t>
+          <t>huancabamba</t>
         </is>
       </c>
     </row>
@@ -7131,12 +7175,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>yamango</t>
+          <t>santa_catalina_de_mossa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Yamango</t>
+          <t>Santa Catalina de Mossa</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -7148,32 +7192,76 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>metodo_coord</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>gps</t>
+          <t>santo_domingo</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>GPS del celular</t>
+          <t>Santo Domingo</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>morropon</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
+          <t>distrito</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>yamango</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Yamango</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>morropon</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
           <t>metodo_coord</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>gps</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>GPS del celular</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>metodo_coord</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
         <is>
           <t>utm</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>Digitar UTM 17S (Este / Norte)</t>
         </is>
@@ -7240,7 +7328,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>202610252255</t>
+          <t>202610260022</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/kobo_ficha_predial/FP_Ficha_Predial_Completa_KOBO.xlsx
+++ b/kobo_ficha_predial/FP_Ficha_Predial_Completa_KOBO.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:N163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,7 @@
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,6 +511,11 @@
           <t>parameters</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>repeat_count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3511,117 +3517,142 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>r_puntos</t>
+          <t>n_puntos</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Puntos de control / vértices del predio</t>
+          <t>N.° de puntos de control / vértices del predio</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Indique cuántos registrará (0 a 50). Para corregir, vuelva aquí y cambie el número.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 50</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Entre 0 y 50</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>pt_gps</t>
+          <t>r_puntos</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Precisión ≤ 10 m.</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Puntos de control / vértices del predio</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>${n_puntos} &gt; 0</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>${n_puntos}</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>select_one pt_tipo</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>pt_tipo</t>
+          <t>pt_gps</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tipo de punto</t>
+          <t>Punto</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Precisión ≤ 10 m.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>select_one pt_tipo</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>r_puntos</t>
+          <t>pt_tipo</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Tipo de punto</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>g_fotos</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>8. Panel fotográfico</t>
+          <t>r_puntos</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>foto_1</t>
+          <t>g_fotos</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Foto 1 – Vista general del predio</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Tome la foto con la cámara del celular (o elija una imagen).</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>max-pixels=1280</t>
+          <t>8. Panel fotográfico</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3664,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>foto_2</t>
+          <t>foto_1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Foto 2 – Cobertura vegetal / uso actual</t>
+          <t>Foto 1 – Vista general del predio</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3660,12 +3691,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>foto_3</t>
+          <t>foto_2</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Foto 3 – Linderos, hitos o accesos</t>
+          <t>Foto 2 – Cobertura vegetal / uso actual</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3687,12 +3718,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>foto_4</t>
+          <t>foto_3</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Foto 4 – Interferencias o detalle relevante</t>
+          <t>Foto 3 – Linderos, hitos o accesos</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3709,110 +3740,137 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>g_fotos</t>
+          <t>foto_4</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Foto 4 – Interferencias o detalle relevante</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Tome la foto con la cámara del celular (o elija una imagen).</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>max-pixels=1280</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>g_firmas</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>9. Conformidad</t>
+          <t>g_fotos</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>firma_prediante</t>
+          <t>g_firmas</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Firma del prediante / titular (conformidad)</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>${consentimiento}='si'</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>max-pixels=800</t>
+          <t>9. Conformidad</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>lugar</t>
+          <t>firma_prediante</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Lugar</t>
+          <t>Firma del prediante / titular (conformidad)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>${consentimiento}='si'</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>signature</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>max-pixels=800</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>g_firmas</t>
+          <t>lugar</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Lugar</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>g_firmas</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>nota_fin</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>Fin de la ficha predial. Pulse «Enviar»: el formulario queda en blanco y vuelve al inicio para registrar el siguiente predio.</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>Use el enlace «En línea-Fuera de línea (envíos múltiples)» de KoboToolbox o KoboCollect.</t>
         </is>
@@ -7328,7 +7386,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>202610260022</t>
+          <t>202610271747</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/kobo_ficha_predial/FP_Ficha_Predial_Completa_KOBO.xlsx
+++ b/kobo_ficha_predial/FP_Ficha_Predial_Completa_KOBO.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N163"/>
+  <dimension ref="A1:N164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3086,341 +3086,366 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>r_afectaciones</t>
+          <t>n_afectaciones</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Afectaciones (OC-01, OC-02…)</t>
+          <t>N.° de obras o bienes afectados</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Indique cuántos registrará (1 a 20). Para corregir, vuelva aquí y cambie el número.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
           <t>${tiene_afectaciones}='si'</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 20</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Entre 1 y 20</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>af_codigo</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>concat('OC-', if(position(..) &lt; 10, '0', ''), position(..))</t>
+          <t>r_afectaciones</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Afectaciones (OC-01, OC-02…)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>${tiene_afectaciones}='si' and ${n_afectaciones} &gt; 0</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>${n_afectaciones}</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>af_nota</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>**${af_codigo}**</t>
+          <t>af_codigo</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>concat('OC-', if(position(..) &lt; 10, '0', ''), position(..))</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>af_descripcion</t>
+          <t>af_nota</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Descripción / uso</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>**${af_codigo}**</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>af_metrado</t>
+          <t>af_descripcion</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Metrado</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>. &gt;= 0</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Valor no negativo</t>
+          <t>Descripción / uso</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>select_one und_medida</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>af_und</t>
+          <t>af_metrado</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Unidad de medida</t>
+          <t>Metrado</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Valor no negativo</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>select_one material</t>
+          <t>select_one und_medida</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>af_material</t>
+          <t>af_und</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Material predominante</t>
+          <t>Unidad de medida</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>select_one conservacion</t>
+          <t>select_one material</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>af_conservacion</t>
+          <t>af_material</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Estado de conservación</t>
+          <t>Material predominante</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>select_one construccion</t>
+          <t>select_one conservacion</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>af_construccion</t>
+          <t>af_conservacion</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Estado de construcción</t>
+          <t>Estado de conservación</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one construccion</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>af_ubicacion</t>
+          <t>af_construccion</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ubicación en el predio</t>
+          <t>Estado de construcción</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>r_afectaciones</t>
+          <t>af_ubicacion</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ubicación en el predio</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>g_liberacion</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>6. Disponibilidad y condición de liberación</t>
+          <t>r_afectaciones</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>select_one aceptacion</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>aceptacion</t>
+          <t>g_liberacion</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Aceptación del titular / prediante</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>6. Disponibilidad y condición de liberación</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>select_one modalidad</t>
+          <t>select_one aceptacion</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>modalidad</t>
+          <t>aceptacion</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Modalidad de disponibilidad</t>
+          <t>Aceptación del titular / prediante</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>select_one conclusion_campo</t>
+          <t>select_one modalidad</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>conclusion_campo</t>
+          <t>modalidad</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Conclusión de campo</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Modalidad de disponibilidad</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>select_one estado_la</t>
+          <t>select_one conclusion_campo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>estado_la_propuesto</t>
+          <t>conclusion_campo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Estado LA propuesto</t>
+          <t>Conclusión de campo</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>select_one tipo_acta</t>
+          <t>select_one estado_la</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>tipo_acta_prevista</t>
+          <t>estado_la_propuesto</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Acta prevista</t>
+          <t>Estado LA propuesto</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one tipo_acta</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>cod_titular_prev</t>
+          <t>tipo_acta_prevista</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Código de titular ya registrado (T0000), si existe</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>regex(., '^T[0-9]{4}$')</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Formato T0000 (T y 4 dígitos)</t>
+          <t>Acta prevista</t>
         </is>
       </c>
     </row>
@@ -3432,254 +3457,254 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>alertas</t>
+          <t>cod_titular_prev</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Observaciones / alertas sociales</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>multiline</t>
+          <t>Código de titular ya registrado (T0000), si existe</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>regex(., '^T[0-9]{4}$')</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Formato T0000 (T y 4 dígitos)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>g_liberacion</t>
+          <t>alertas</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Observaciones / alertas sociales</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>multiline</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>g_croquis</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>7. Croquis del predio y puntos de control</t>
+          <t>g_liberacion</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>croquis</t>
+          <t>g_croquis</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Croquis del predio (dibuje: norte, linderos, accesos, vértices)</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>max-pixels=1280</t>
+          <t>7. Croquis del predio y puntos de control</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>g_croquis</t>
+          <t>croquis</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Croquis del predio (dibuje: norte, linderos, accesos, vértices)</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>max-pixels=1280</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>n_puntos</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>N.° de puntos de control / vértices del predio</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Indique cuántos registrará (0 a 50). Para corregir, vuelva aquí y cambie el número.</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 50</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Entre 0 y 50</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>g_croquis</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>begin_repeat</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>r_puntos</t>
+          <t>n_puntos</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Puntos de control / vértices del predio</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>${n_puntos} &gt; 0</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>${n_puntos}</t>
+          <t>N.° de puntos de control / vértices del predio</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Indique cuántos registrará (0 a 50). Para corregir, vuelva aquí y cambie el número.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 50</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Entre 0 y 50</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>begin_repeat</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>pt_gps</t>
+          <t>r_puntos</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Precisión ≤ 10 m.</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Puntos de control / vértices del predio</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>${n_puntos} &gt; 0</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>${n_puntos}</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>select_one pt_tipo</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>pt_tipo</t>
+          <t>pt_gps</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tipo de punto</t>
+          <t>Punto</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Precisión ≤ 10 m.</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>end_repeat</t>
+          <t>select_one pt_tipo</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>r_puntos</t>
+          <t>pt_tipo</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Tipo de punto</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_repeat</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>g_fotos</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>8. Panel fotográfico</t>
+          <t>r_puntos</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>foto_1</t>
+          <t>g_fotos</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Foto 1 – Vista general del predio</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Tome la foto con la cámara del celular (o elija una imagen).</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>max-pixels=1280</t>
+          <t>8. Panel fotográfico</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3716,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>foto_2</t>
+          <t>foto_1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Foto 2 – Cobertura vegetal / uso actual</t>
+          <t>Foto 1 – Vista general del predio</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3718,12 +3743,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>foto_3</t>
+          <t>foto_2</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Foto 3 – Linderos, hitos o accesos</t>
+          <t>Foto 2 – Cobertura vegetal / uso actual</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3745,12 +3770,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>foto_4</t>
+          <t>foto_3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Foto 4 – Interferencias o detalle relevante</t>
+          <t>Foto 3 – Linderos, hitos o accesos</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3767,110 +3792,137 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>g_fotos</t>
+          <t>foto_4</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Foto 4 – Interferencias o detalle relevante</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Tome la foto con la cámara del celular (o elija una imagen).</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>max-pixels=1280</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>end_group</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>g_firmas</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>9. Conformidad</t>
+          <t>g_fotos</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>firma_prediante</t>
+          <t>g_firmas</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Firma del prediante / titular (conformidad)</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>${consentimiento}='si'</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>max-pixels=800</t>
+          <t>9. Conformidad</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>lugar</t>
+          <t>firma_prediante</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Lugar</t>
+          <t>Firma del prediante / titular (conformidad)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>${consentimiento}='si'</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>signature</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>max-pixels=800</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>end_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>g_firmas</t>
+          <t>lugar</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Lugar</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>g_firmas</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>nota_fin</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Fin de la ficha predial. Pulse «Enviar»: el formulario queda en blanco y vuelve al inicio para registrar el siguiente predio.</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>Use el enlace «En línea-Fuera de línea (envíos múltiples)» de KoboToolbox o KoboCollect.</t>
         </is>
@@ -7386,7 +7438,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>202610271747</t>
+          <t>202610271828</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
